--- a/VerveStacks_IDN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IDN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{516B7AD8-2B1F-48AE-B870-DAC132C5E163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F254FF6E-F27D-41B2-9715-709239FDC8E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -523,337 +523,337 @@
     <t>efficiency</t>
   </si>
   <si>
-    <t>g_ID1-275-w721685825-275</t>
-  </si>
-  <si>
-    <t>g_ID11-500-ID10-500</t>
-  </si>
-  <si>
-    <t>g_ID12-500-ID10-500</t>
-  </si>
-  <si>
-    <t>g_ID13-500-ID16-500</t>
-  </si>
-  <si>
-    <t>g_ID13-500-ID22-500</t>
-  </si>
-  <si>
-    <t>g_ID13-500-w960747902-500</t>
-  </si>
-  <si>
-    <t>g_ID14-500-ID17-500</t>
-  </si>
-  <si>
-    <t>g_ID16-500-ID19-500</t>
-  </si>
-  <si>
-    <t>g_ID18-500-w662591948-500</t>
-  </si>
-  <si>
-    <t>g_ID20-500-ID19-500</t>
-  </si>
-  <si>
-    <t>g_ID21-500-ID20-500</t>
-  </si>
-  <si>
-    <t>g_ID22-500-ID25-500</t>
-  </si>
-  <si>
-    <t>g_ID22-500-w271376037-500</t>
-  </si>
-  <si>
-    <t>g_ID26-500-w264550744-500</t>
-  </si>
-  <si>
-    <t>g_ID27-500-ID28-500</t>
-  </si>
-  <si>
-    <t>g_ID31-500-w166633831-500</t>
-  </si>
-  <si>
-    <t>g_ID31-500-w689263666-500</t>
-  </si>
-  <si>
-    <t>g_ID33-500-w264410236-500</t>
-  </si>
-  <si>
-    <t>g_ID33-500-w314452486-500</t>
-  </si>
-  <si>
-    <t>g_ID34-500-w265568001-500</t>
-  </si>
-  <si>
-    <t>g_ID36-500-w265318414-500</t>
-  </si>
-  <si>
-    <t>g_ID4-275-ID3-275</t>
-  </si>
-  <si>
-    <t>g_ID5-275-w928928133-275</t>
-  </si>
-  <si>
-    <t>g_ID6-275-w928928133-275</t>
-  </si>
-  <si>
-    <t>g_ID7-275-w930719092-275</t>
-  </si>
-  <si>
-    <t>g_ID7-275-w939542521-275</t>
-  </si>
-  <si>
-    <t>g_ID8-275-w1316786278-275</t>
-  </si>
-  <si>
-    <t>g_w1013653012-500-w960747936-500</t>
-  </si>
-  <si>
-    <t>g_w1308433899-500-ID36-500</t>
-  </si>
-  <si>
-    <t>g_w1312287191-275-ID7-275</t>
-  </si>
-  <si>
-    <t>g_w159940153-500-ID16-500</t>
-  </si>
-  <si>
-    <t>g_w161960924-500-ID33-500</t>
-  </si>
-  <si>
-    <t>g_w161960924-500-w966209515-500</t>
-  </si>
-  <si>
-    <t>g_w161960933-500-w161960924-500</t>
-  </si>
-  <si>
-    <t>g_w161960933-500-w399038181-500</t>
-  </si>
-  <si>
-    <t>g_w161965853-500-ID11-500</t>
-  </si>
-  <si>
-    <t>g_w161965853-500-w966209515-500</t>
-  </si>
-  <si>
-    <t>g_w166633831-500-ID28-500</t>
-  </si>
-  <si>
-    <t>g_w166633831-500-w1308433899-500</t>
-  </si>
-  <si>
-    <t>g_w166633831-500-w265568001-500</t>
-  </si>
-  <si>
-    <t>g_w166633831-500-w398909640-500</t>
-  </si>
-  <si>
-    <t>g_w169444592-500-ID11-500</t>
-  </si>
-  <si>
-    <t>g_w169444592-500-ID12-500</t>
-  </si>
-  <si>
-    <t>g_w169444592-500-w399038181-500</t>
-  </si>
-  <si>
-    <t>g_w261185002-500-ID29-500</t>
-  </si>
-  <si>
-    <t>g_w261185002-500-ID31-500</t>
-  </si>
-  <si>
-    <t>g_w261185002-500-w1013653012-500</t>
-  </si>
-  <si>
-    <t>g_w261185002-500-w689263666-500</t>
-  </si>
-  <si>
-    <t>g_w264410236-500-w261185002-500</t>
-  </si>
-  <si>
-    <t>g_w264410236-500-w769617021-500</t>
-  </si>
-  <si>
-    <t>g_w264550744-500-w264410236-500</t>
-  </si>
-  <si>
-    <t>g_w265318414-500-ID38-500</t>
-  </si>
-  <si>
-    <t>g_w265568001-500-w340978681-500</t>
-  </si>
-  <si>
-    <t>g_w267626657-500-ID36-500</t>
-  </si>
-  <si>
-    <t>g_w267626657-500-ID37-500</t>
-  </si>
-  <si>
-    <t>g_w271376037-500-ID21-500</t>
-  </si>
-  <si>
-    <t>g_w271376037-500-ID24-500</t>
-  </si>
-  <si>
-    <t>g_w310958602-275-w754096394-275</t>
-  </si>
-  <si>
-    <t>g_w314452486-500-w267626657-500</t>
-  </si>
-  <si>
-    <t>g_w337039411-275-w310695690-275</t>
-  </si>
-  <si>
-    <t>g_w340205049-275-w754073846-275</t>
-  </si>
-  <si>
-    <t>g_w340205049-275-w754096394-275</t>
-  </si>
-  <si>
-    <t>g_w340978681-500-ID35-500</t>
-  </si>
-  <si>
-    <t>g_w340978681-500-ID38-500</t>
-  </si>
-  <si>
-    <t>g_w398909640-500-w265568001-500</t>
-  </si>
-  <si>
-    <t>g_w399038181-500-w662591948-500</t>
-  </si>
-  <si>
-    <t>g_w399100034-500-w960747902-500</t>
-  </si>
-  <si>
-    <t>g_w399100034-500-w960747936-500</t>
-  </si>
-  <si>
-    <t>g_w399100035-500-w264550744-500</t>
-  </si>
-  <si>
-    <t>g_w469888049-275-w928928133-275</t>
-  </si>
-  <si>
-    <t>g_w527900241-275-w528189342-275</t>
-  </si>
-  <si>
-    <t>g_w527900241-275-w931931133-275</t>
-  </si>
-  <si>
-    <t>g_w544403426-230-ID9-230</t>
-  </si>
-  <si>
-    <t>g_w544403431-230-w759130125-230</t>
-  </si>
-  <si>
-    <t>g_w562061281-275-ID2-275</t>
-  </si>
-  <si>
-    <t>g_w604684007-500-w161960933-500</t>
-  </si>
-  <si>
-    <t>g_w604684007-500-w169444592-500</t>
-  </si>
-  <si>
-    <t>g_w614955990-230-ID9-230</t>
-  </si>
-  <si>
-    <t>g_w614955993-230-w544403431-230</t>
-  </si>
-  <si>
-    <t>g_w614955993-230-w614955990-230</t>
-  </si>
-  <si>
-    <t>g_w615581232-275-w615581242-275</t>
-  </si>
-  <si>
-    <t>g_w615581242-275-w1193553154-275</t>
-  </si>
-  <si>
-    <t>g_w615581270-275-w615581232-275</t>
-  </si>
-  <si>
-    <t>g_w629512849-500-ID37-500</t>
-  </si>
-  <si>
-    <t>g_w662591948-500-ID15-500</t>
-  </si>
-  <si>
-    <t>g_w689263666-500-ID27-500</t>
-  </si>
-  <si>
-    <t>g_w689263666-500-ID30-500</t>
-  </si>
-  <si>
-    <t>g_w689263666-500-ID31-500</t>
-  </si>
-  <si>
-    <t>g_w721674155-275-w310958602-275</t>
-  </si>
-  <si>
-    <t>g_w721674155-275-w469888049-275</t>
-  </si>
-  <si>
-    <t>g_w736595653-275-ID3-275</t>
-  </si>
-  <si>
-    <t>g_w736595653-500-w1186182648-500</t>
-  </si>
-  <si>
-    <t>g_w753733608-275-w610198177-275</t>
-  </si>
-  <si>
-    <t>g_w754178666-275-w310695690-275</t>
-  </si>
-  <si>
-    <t>g_w754178667-275-w310958602-275</t>
-  </si>
-  <si>
-    <t>g_w769617021-500-w261185002-500</t>
-  </si>
-  <si>
-    <t>g_w841499143-275-w528189342-275</t>
-  </si>
-  <si>
-    <t>g_w841499143-275-w930719092-275</t>
-  </si>
-  <si>
-    <t>g_w926254403-500-ID25-500</t>
-  </si>
-  <si>
-    <t>g_w928220391-275-w721685825-275</t>
-  </si>
-  <si>
-    <t>g_w928928133-275-w939542521-275</t>
-  </si>
-  <si>
-    <t>g_w931931121-275-w1316786278-275</t>
-  </si>
-  <si>
-    <t>g_w931931121-275-w1316876158-275</t>
-  </si>
-  <si>
-    <t>g_w931931133-275-w1316786278-275</t>
-  </si>
-  <si>
-    <t>g_w943539373-275-w946191122-275</t>
-  </si>
-  <si>
-    <t>g_w943539373-500-w1186182648-500</t>
-  </si>
-  <si>
-    <t>g_w946191122-275-w753733608-275</t>
-  </si>
-  <si>
-    <t>g_w960747902-500-ID23-500</t>
-  </si>
-  <si>
-    <t>g_w960747936-500-w399100035-500</t>
-  </si>
-  <si>
-    <t>g_w966209515-500-ID26-500</t>
-  </si>
-  <si>
-    <t>g_w966209515-500-w926254403-500</t>
+    <t>g_ID1-275_IDN-w721685825-275_IDN</t>
+  </si>
+  <si>
+    <t>g_ID11-500_IDN-ID10-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID12-500_IDN-ID10-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID13-500_IDN-ID16-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID13-500_IDN-ID22-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID13-500_IDN-w960747902-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID14-500_IDN-ID17-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID16-500_IDN-ID19-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID18-500_IDN-w662591948-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID20-500_IDN-ID19-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID21-500_IDN-ID20-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID22-500_IDN-ID25-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID22-500_IDN-w271376037-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID26-500_IDN-w264550744-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID27-500_IDN-ID28-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID31-500_IDN-w166633831-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID31-500_IDN-w689263666-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID33-500_IDN-w264410236-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID33-500_IDN-w314452486-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID34-500_IDN-w265568001-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID36-500_IDN-w265318414-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID4-275_IDN-ID3-275_IDN</t>
+  </si>
+  <si>
+    <t>g_ID5-275_IDN-w928928133-275_IDN</t>
+  </si>
+  <si>
+    <t>g_ID6-275_IDN-w928928133-275_IDN</t>
+  </si>
+  <si>
+    <t>g_ID7-275_IDN-w930719092-275_IDN</t>
+  </si>
+  <si>
+    <t>g_ID7-275_IDN-w939542521-275_IDN</t>
+  </si>
+  <si>
+    <t>g_ID8-275_IDN-w1316786278-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w1013653012-500_IDN-w960747936-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w1308433899-500_IDN-ID36-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w1312287191-275_IDN-ID7-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w159940153-500_IDN-ID16-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w161960924-500_IDN-ID33-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w161960924-500_IDN-w966209515-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w161960933-500_IDN-w161960924-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w161960933-500_IDN-w399038181-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w161965853-500_IDN-ID11-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w161965853-500_IDN-w966209515-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w166633831-500_IDN-ID28-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w166633831-500_IDN-w1308433899-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w166633831-500_IDN-w265568001-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w166633831-500_IDN-w398909640-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w169444592-500_IDN-ID11-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w169444592-500_IDN-ID12-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w169444592-500_IDN-w399038181-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w261185002-500_IDN-ID29-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w261185002-500_IDN-ID31-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w261185002-500_IDN-w1013653012-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w261185002-500_IDN-w689263666-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w264410236-500_IDN-w261185002-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w264410236-500_IDN-w769617021-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w264550744-500_IDN-w264410236-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w265318414-500_IDN-ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w265568001-500_IDN-w340978681-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w267626657-500_IDN-ID36-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w267626657-500_IDN-ID37-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w271376037-500_IDN-ID21-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w271376037-500_IDN-ID24-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w310958602-275_IDN-w754096394-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w314452486-500_IDN-w267626657-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w337039411-275_IDN-w310695690-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w340205049-275_IDN-w754073846-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w340205049-275_IDN-w754096394-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w340978681-500_IDN-ID35-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w340978681-500_IDN-ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w398909640-500_IDN-w265568001-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w399038181-500_IDN-w662591948-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w399100034-500_IDN-w960747902-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w399100034-500_IDN-w960747936-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w399100035-500_IDN-w264550744-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w469888049-275_IDN-w928928133-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w527900241-275_IDN-w528189342-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w527900241-275_IDN-w931931133-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w544403426-230_IDN-ID9-230_IDN</t>
+  </si>
+  <si>
+    <t>g_w544403431-230_IDN-w759130125-230_IDN</t>
+  </si>
+  <si>
+    <t>g_w562061281-275_IDN-ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w604684007-500_IDN-w161960933-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w604684007-500_IDN-w169444592-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w614955990-230_IDN-ID9-230_IDN</t>
+  </si>
+  <si>
+    <t>g_w614955993-230_IDN-w544403431-230_IDN</t>
+  </si>
+  <si>
+    <t>g_w614955993-230_IDN-w614955990-230_IDN</t>
+  </si>
+  <si>
+    <t>g_w615581232-275_IDN-w615581242-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w615581242-275_IDN-w1193553154-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w615581270-275_IDN-w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w629512849-500_IDN-ID37-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w662591948-500_IDN-ID15-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w689263666-500_IDN-ID27-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w689263666-500_IDN-ID30-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w689263666-500_IDN-ID31-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w721674155-275_IDN-w310958602-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w721674155-275_IDN-w469888049-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w736595653-275_IDN-ID3-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w736595653-500_IDN-w1186182648-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w753733608-275_IDN-w610198177-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w754178666-275_IDN-w310695690-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w754178667-275_IDN-w310958602-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w769617021-500_IDN-w261185002-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w841499143-275_IDN-w528189342-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w841499143-275_IDN-w930719092-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w926254403-500_IDN-ID25-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w928220391-275_IDN-w721685825-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w928928133-275_IDN-w939542521-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w931931121-275_IDN-w1316786278-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w931931121-275_IDN-w1316876158-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w931931133-275_IDN-w1316786278-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w943539373-275_IDN-w946191122-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w943539373-500_IDN-w1186182648-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w946191122-275_IDN-w753733608-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w960747902-500_IDN-ID23-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w960747936-500_IDN-w399100035-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w966209515-500_IDN-ID26-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w966209515-500_IDN-w926254403-500_IDN</t>
   </si>
   <si>
     <t>~tfm_ins-at</t>
@@ -868,7 +868,7 @@
     <t>lim_type</t>
   </si>
   <si>
-    <t>e_demand_w161960924-500</t>
+    <t>e_demand_w161960924-500_IDN</t>
   </si>
   <si>
     <t>elc_buildings,elc_transport,elc_industry,elc_roadtransport</t>
@@ -877,121 +877,121 @@
     <t>lo</t>
   </si>
   <si>
-    <t>e_demand_w161960933-500</t>
-  </si>
-  <si>
-    <t>e_demand_w166633831-500</t>
-  </si>
-  <si>
-    <t>e_demand_w264410236-500</t>
-  </si>
-  <si>
-    <t>e_demand_w271376037-500</t>
-  </si>
-  <si>
-    <t>e_demand_w604684007-500</t>
-  </si>
-  <si>
-    <t>e_demand_ID36-500</t>
-  </si>
-  <si>
-    <t>e_demand_ID34-500</t>
-  </si>
-  <si>
-    <t>e_demand_ID35-500</t>
-  </si>
-  <si>
-    <t>e_demand_ID17-500</t>
-  </si>
-  <si>
-    <t>ev_battery_w161960924-500</t>
-  </si>
-  <si>
-    <t>ev_battery_w161960933-500</t>
-  </si>
-  <si>
-    <t>ev_battery_w166633831-500</t>
-  </si>
-  <si>
-    <t>ev_battery_w264410236-500</t>
-  </si>
-  <si>
-    <t>ev_battery_w271376037-500</t>
-  </si>
-  <si>
-    <t>ev_battery_w604684007-500</t>
-  </si>
-  <si>
-    <t>ev_battery_ID36-500</t>
-  </si>
-  <si>
-    <t>ev_battery_ID34-500</t>
-  </si>
-  <si>
-    <t>ev_battery_ID35-500</t>
-  </si>
-  <si>
-    <t>ev_battery_ID17-500</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w161960924-500</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w161960933-500</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w166633831-500</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w264410236-500</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w271376037-500</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w604684007-500</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_ID36-500</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_ID34-500</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_ID35-500</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_ID17-500</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w161960924-500</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w161960933-500</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w166633831-500</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w264410236-500</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w271376037-500</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w604684007-500</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_ID36-500</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_ID34-500</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_ID35-500</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_ID17-500</t>
+    <t>e_demand_w161960933-500_IDN</t>
+  </si>
+  <si>
+    <t>e_demand_w166633831-500_IDN</t>
+  </si>
+  <si>
+    <t>e_demand_w264410236-500_IDN</t>
+  </si>
+  <si>
+    <t>e_demand_w271376037-500_IDN</t>
+  </si>
+  <si>
+    <t>e_demand_w604684007-500_IDN</t>
+  </si>
+  <si>
+    <t>e_demand_ID36-500_IDN</t>
+  </si>
+  <si>
+    <t>e_demand_ID34-500_IDN</t>
+  </si>
+  <si>
+    <t>e_demand_ID35-500_IDN</t>
+  </si>
+  <si>
+    <t>e_demand_ID17-500_IDN</t>
+  </si>
+  <si>
+    <t>ev_battery_w161960924-500_IDN</t>
+  </si>
+  <si>
+    <t>ev_battery_w161960933-500_IDN</t>
+  </si>
+  <si>
+    <t>ev_battery_w166633831-500_IDN</t>
+  </si>
+  <si>
+    <t>ev_battery_w264410236-500_IDN</t>
+  </si>
+  <si>
+    <t>ev_battery_w271376037-500_IDN</t>
+  </si>
+  <si>
+    <t>ev_battery_w604684007-500_IDN</t>
+  </si>
+  <si>
+    <t>ev_battery_ID36-500_IDN</t>
+  </si>
+  <si>
+    <t>ev_battery_ID34-500_IDN</t>
+  </si>
+  <si>
+    <t>ev_battery_ID35-500_IDN</t>
+  </si>
+  <si>
+    <t>ev_battery_ID17-500_IDN</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_w161960924-500_IDN</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_w161960933-500_IDN</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_w166633831-500_IDN</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_w264410236-500_IDN</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_w271376037-500_IDN</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_w604684007-500_IDN</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_ID36-500_IDN</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_ID34-500_IDN</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_ID35-500_IDN</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_ID17-500_IDN</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_w161960924-500_IDN</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_w161960933-500_IDN</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_w166633831-500_IDN</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_w264410236-500_IDN</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_w271376037-500_IDN</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_w604684007-500_IDN</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_ID36-500_IDN</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_ID34-500_IDN</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_ID35-500_IDN</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_ID17-500_IDN</t>
   </si>
   <si>
     <t>~tfm_topins</t>
@@ -1000,2599 +1000,2599 @@
     <t>io</t>
   </si>
   <si>
-    <t>e_w161960924-500</t>
+    <t>e_w161960924-500_IDN</t>
   </si>
   <si>
     <t>IN</t>
   </si>
   <si>
-    <t>e_w161960933-500</t>
-  </si>
-  <si>
-    <t>e_w166633831-500</t>
-  </si>
-  <si>
-    <t>e_w264410236-500</t>
-  </si>
-  <si>
-    <t>e_w271376037-500</t>
-  </si>
-  <si>
-    <t>e_w604684007-500</t>
-  </si>
-  <si>
-    <t>e_ID36-500</t>
-  </si>
-  <si>
-    <t>e_ID34-500</t>
-  </si>
-  <si>
-    <t>e_ID35-500</t>
-  </si>
-  <si>
-    <t>e_ID17-500</t>
+    <t>e_w161960933-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w166633831-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w264410236-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w271376037-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w604684007-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID36-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID34-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID35-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID17-500_IDN</t>
   </si>
   <si>
     <t>region</t>
   </si>
   <si>
-    <t>Bioenergy + CCUS_w610198177-275</t>
-  </si>
-  <si>
-    <t>e_w610198177-275</t>
+    <t>Bioenergy + CCUS_w610198177-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w610198177-275_IDN</t>
   </si>
   <si>
     <t>OUT</t>
   </si>
   <si>
-    <t>Bioenergy - Large scale unit_w610198177-275</t>
-  </si>
-  <si>
-    <t>CCGT_w610198177-275</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_w610198177-275</t>
-  </si>
-  <si>
-    <t>Coal + CCS_w610198177-275</t>
-  </si>
-  <si>
-    <t>Gas turbine_w610198177-275</t>
-  </si>
-  <si>
-    <t>IGCC_w610198177-275</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_w610198177-275</t>
-  </si>
-  <si>
-    <t>Nuclear large_w610198177-275</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_w610198177-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_w610198177-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_w610198177-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_w610198177-275</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_w544403426-230</t>
-  </si>
-  <si>
-    <t>e_w544403426-230</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_w544403426-230</t>
-  </si>
-  <si>
-    <t>CCGT_w544403426-230</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_w544403426-230</t>
-  </si>
-  <si>
-    <t>Coal + CCS_w544403426-230</t>
-  </si>
-  <si>
-    <t>Gas turbine_w544403426-230</t>
-  </si>
-  <si>
-    <t>IGCC_w544403426-230</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_w544403426-230</t>
-  </si>
-  <si>
-    <t>Nuclear large_w544403426-230</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_w544403426-230</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_w544403426-230</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_w544403426-230</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_w544403426-230</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_w721685825-275</t>
-  </si>
-  <si>
-    <t>e_w721685825-275</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_w721685825-275</t>
-  </si>
-  <si>
-    <t>CCGT_w721685825-275</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_w721685825-275</t>
-  </si>
-  <si>
-    <t>Coal + CCS_w721685825-275</t>
-  </si>
-  <si>
-    <t>Gas turbine_w721685825-275</t>
-  </si>
-  <si>
-    <t>IGCC_w721685825-275</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_w721685825-275</t>
-  </si>
-  <si>
-    <t>Nuclear large_w721685825-275</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_w721685825-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_w721685825-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_w721685825-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_w721685825-275</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_w615581232-275</t>
-  </si>
-  <si>
-    <t>e_w615581232-275</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_w615581232-275</t>
-  </si>
-  <si>
-    <t>CCGT_w615581232-275</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_w615581232-275</t>
-  </si>
-  <si>
-    <t>Coal + CCS_w615581232-275</t>
-  </si>
-  <si>
-    <t>Gas turbine_w615581232-275</t>
-  </si>
-  <si>
-    <t>IGCC_w615581232-275</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_w615581232-275</t>
-  </si>
-  <si>
-    <t>Nuclear large_w615581232-275</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_w615581232-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_w615581232-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_w615581232-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_w615581232-275</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_ID2-275</t>
-  </si>
-  <si>
-    <t>e_ID2-275</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_ID2-275</t>
-  </si>
-  <si>
-    <t>CCGT_ID2-275</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_ID2-275</t>
-  </si>
-  <si>
-    <t>Coal + CCS_ID2-275</t>
-  </si>
-  <si>
-    <t>Gas turbine_ID2-275</t>
-  </si>
-  <si>
-    <t>IGCC_ID2-275</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_ID2-275</t>
-  </si>
-  <si>
-    <t>Nuclear large_ID2-275</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_ID2-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_ID2-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_ID2-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_ID2-275</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_ID38-500</t>
-  </si>
-  <si>
-    <t>e_ID38-500</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_ID38-500</t>
-  </si>
-  <si>
-    <t>CCGT_ID38-500</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_ID38-500</t>
-  </si>
-  <si>
-    <t>Coal + CCS_ID38-500</t>
-  </si>
-  <si>
-    <t>Gas turbine_ID38-500</t>
-  </si>
-  <si>
-    <t>IGCC_ID38-500</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_ID38-500</t>
-  </si>
-  <si>
-    <t>Nuclear large_ID38-500</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_ID38-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_ID38-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_ID38-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_ID38-500</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_w337039411-275</t>
-  </si>
-  <si>
-    <t>e_w337039411-275</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_w337039411-275</t>
-  </si>
-  <si>
-    <t>CCGT_w337039411-275</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_w337039411-275</t>
-  </si>
-  <si>
-    <t>Coal + CCS_w337039411-275</t>
-  </si>
-  <si>
-    <t>Gas turbine_w337039411-275</t>
-  </si>
-  <si>
-    <t>IGCC_w337039411-275</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_w337039411-275</t>
-  </si>
-  <si>
-    <t>Nuclear large_w337039411-275</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_w337039411-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_w337039411-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_w337039411-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_w337039411-275</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_w340205049-275</t>
-  </si>
-  <si>
-    <t>e_w340205049-275</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_w340205049-275</t>
-  </si>
-  <si>
-    <t>CCGT_w340205049-275</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_w340205049-275</t>
-  </si>
-  <si>
-    <t>Coal + CCS_w340205049-275</t>
-  </si>
-  <si>
-    <t>Gas turbine_w340205049-275</t>
-  </si>
-  <si>
-    <t>IGCC_w340205049-275</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_w340205049-275</t>
-  </si>
-  <si>
-    <t>Nuclear large_w340205049-275</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_w340205049-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_w340205049-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_w340205049-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_w340205049-275</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_ID12-500</t>
-  </si>
-  <si>
-    <t>e_ID12-500</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_ID12-500</t>
-  </si>
-  <si>
-    <t>CCGT_ID12-500</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_ID12-500</t>
-  </si>
-  <si>
-    <t>Coal + CCS_ID12-500</t>
-  </si>
-  <si>
-    <t>Gas turbine_ID12-500</t>
-  </si>
-  <si>
-    <t>IGCC_ID12-500</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_ID12-500</t>
-  </si>
-  <si>
-    <t>Nuclear large_ID12-500</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_ID12-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_ID12-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_ID12-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_ID12-500</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_w340978681-500</t>
-  </si>
-  <si>
-    <t>e_w340978681-500</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_w340978681-500</t>
-  </si>
-  <si>
-    <t>CCGT_w340978681-500</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_w340978681-500</t>
-  </si>
-  <si>
-    <t>Coal + CCS_w340978681-500</t>
-  </si>
-  <si>
-    <t>Gas turbine_w340978681-500</t>
-  </si>
-  <si>
-    <t>IGCC_w340978681-500</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_w340978681-500</t>
-  </si>
-  <si>
-    <t>Nuclear large_w340978681-500</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_w340978681-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_w340978681-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_w340978681-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_w340978681-500</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_ID34-500</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_ID34-500</t>
-  </si>
-  <si>
-    <t>CCGT_ID34-500</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_ID34-500</t>
-  </si>
-  <si>
-    <t>Coal + CCS_ID34-500</t>
-  </si>
-  <si>
-    <t>Gas turbine_ID34-500</t>
-  </si>
-  <si>
-    <t>IGCC_ID34-500</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_ID34-500</t>
-  </si>
-  <si>
-    <t>Nuclear large_ID34-500</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_ID34-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_ID34-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_ID34-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_ID34-500</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_w960747902-500</t>
-  </si>
-  <si>
-    <t>e_w960747902-500</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_w960747902-500</t>
-  </si>
-  <si>
-    <t>CCGT_w960747902-500</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_w960747902-500</t>
-  </si>
-  <si>
-    <t>Coal + CCS_w960747902-500</t>
-  </si>
-  <si>
-    <t>Gas turbine_w960747902-500</t>
-  </si>
-  <si>
-    <t>IGCC_w960747902-500</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_w960747902-500</t>
-  </si>
-  <si>
-    <t>Nuclear large_w960747902-500</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_w960747902-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_w960747902-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_w960747902-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_w960747902-500</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_w562061281-275</t>
-  </si>
-  <si>
-    <t>e_w562061281-275</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_w562061281-275</t>
-  </si>
-  <si>
-    <t>CCGT_w562061281-275</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_w562061281-275</t>
-  </si>
-  <si>
-    <t>Coal + CCS_w562061281-275</t>
-  </si>
-  <si>
-    <t>Gas turbine_w562061281-275</t>
-  </si>
-  <si>
-    <t>IGCC_w562061281-275</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_w562061281-275</t>
-  </si>
-  <si>
-    <t>Nuclear large_w562061281-275</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_w562061281-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_w562061281-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_w562061281-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_w562061281-275</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_ID15-500</t>
-  </si>
-  <si>
-    <t>e_ID15-500</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_ID15-500</t>
-  </si>
-  <si>
-    <t>CCGT_ID15-500</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_ID15-500</t>
-  </si>
-  <si>
-    <t>Coal + CCS_ID15-500</t>
-  </si>
-  <si>
-    <t>Gas turbine_ID15-500</t>
-  </si>
-  <si>
-    <t>IGCC_ID15-500</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_ID15-500</t>
-  </si>
-  <si>
-    <t>Nuclear large_ID15-500</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_ID15-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_ID15-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_ID15-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_ID15-500</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_ID13-500</t>
-  </si>
-  <si>
-    <t>e_ID13-500</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_ID13-500</t>
-  </si>
-  <si>
-    <t>CCGT_ID13-500</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_ID13-500</t>
-  </si>
-  <si>
-    <t>Coal + CCS_ID13-500</t>
-  </si>
-  <si>
-    <t>Gas turbine_ID13-500</t>
-  </si>
-  <si>
-    <t>IGCC_ID13-500</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_ID13-500</t>
-  </si>
-  <si>
-    <t>Nuclear large_ID13-500</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_ID13-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_ID13-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_ID13-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_ID13-500</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_ID23-500</t>
-  </si>
-  <si>
-    <t>e_ID23-500</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_ID23-500</t>
-  </si>
-  <si>
-    <t>CCGT_ID23-500</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_ID23-500</t>
-  </si>
-  <si>
-    <t>Coal + CCS_ID23-500</t>
-  </si>
-  <si>
-    <t>Gas turbine_ID23-500</t>
-  </si>
-  <si>
-    <t>IGCC_ID23-500</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_ID23-500</t>
-  </si>
-  <si>
-    <t>Nuclear large_ID23-500</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_ID23-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_ID23-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_ID23-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_ID23-500</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_w736595653-500</t>
-  </si>
-  <si>
-    <t>e_w736595653-500</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_w736595653-500</t>
-  </si>
-  <si>
-    <t>CCGT_w736595653-500</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_w736595653-500</t>
-  </si>
-  <si>
-    <t>Coal + CCS_w736595653-500</t>
-  </si>
-  <si>
-    <t>Gas turbine_w736595653-500</t>
-  </si>
-  <si>
-    <t>IGCC_w736595653-500</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_w736595653-500</t>
-  </si>
-  <si>
-    <t>Nuclear large_w736595653-500</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_w736595653-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_w736595653-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_w736595653-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_w736595653-500</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_w736595653-275</t>
-  </si>
-  <si>
-    <t>e_w736595653-275</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_w736595653-275</t>
-  </si>
-  <si>
-    <t>CCGT_w736595653-275</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_w736595653-275</t>
-  </si>
-  <si>
-    <t>Coal + CCS_w736595653-275</t>
-  </si>
-  <si>
-    <t>Gas turbine_w736595653-275</t>
-  </si>
-  <si>
-    <t>IGCC_w736595653-275</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_w736595653-275</t>
-  </si>
-  <si>
-    <t>Nuclear large_w736595653-275</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_w736595653-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_w736595653-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_w736595653-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_w736595653-275</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_ID3-275</t>
-  </si>
-  <si>
-    <t>e_ID3-275</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_ID3-275</t>
-  </si>
-  <si>
-    <t>CCGT_ID3-275</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_ID3-275</t>
-  </si>
-  <si>
-    <t>Coal + CCS_ID3-275</t>
-  </si>
-  <si>
-    <t>Gas turbine_ID3-275</t>
-  </si>
-  <si>
-    <t>IGCC_ID3-275</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_ID3-275</t>
-  </si>
-  <si>
-    <t>Nuclear large_ID3-275</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_ID3-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_ID3-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_ID3-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_ID3-275</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_w615581270-275</t>
-  </si>
-  <si>
-    <t>e_w615581270-275</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_w615581270-275</t>
-  </si>
-  <si>
-    <t>CCGT_w615581270-275</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_w615581270-275</t>
-  </si>
-  <si>
-    <t>Coal + CCS_w615581270-275</t>
-  </si>
-  <si>
-    <t>Gas turbine_w615581270-275</t>
-  </si>
-  <si>
-    <t>IGCC_w615581270-275</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_w615581270-275</t>
-  </si>
-  <si>
-    <t>Nuclear large_w615581270-275</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_w615581270-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_w615581270-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_w615581270-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_w615581270-275</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_w161960924-500</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_w161960924-500</t>
-  </si>
-  <si>
-    <t>CCGT_w161960924-500</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_w161960924-500</t>
-  </si>
-  <si>
-    <t>Coal + CCS_w161960924-500</t>
-  </si>
-  <si>
-    <t>Gas turbine_w161960924-500</t>
-  </si>
-  <si>
-    <t>IGCC_w161960924-500</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_w161960924-500</t>
-  </si>
-  <si>
-    <t>Nuclear large_w161960924-500</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_w161960924-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_w161960924-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_w161960924-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_w161960924-500</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_w166633831-500</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_w166633831-500</t>
-  </si>
-  <si>
-    <t>CCGT_w166633831-500</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_w166633831-500</t>
-  </si>
-  <si>
-    <t>Coal + CCS_w166633831-500</t>
-  </si>
-  <si>
-    <t>Gas turbine_w166633831-500</t>
-  </si>
-  <si>
-    <t>IGCC_w166633831-500</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_w166633831-500</t>
-  </si>
-  <si>
-    <t>Nuclear large_w166633831-500</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_w166633831-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_w166633831-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_w166633831-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_w166633831-500</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_ID14-500</t>
-  </si>
-  <si>
-    <t>e_ID14-500</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_ID14-500</t>
-  </si>
-  <si>
-    <t>CCGT_ID14-500</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_ID14-500</t>
-  </si>
-  <si>
-    <t>Coal + CCS_ID14-500</t>
-  </si>
-  <si>
-    <t>Gas turbine_ID14-500</t>
-  </si>
-  <si>
-    <t>IGCC_ID14-500</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_ID14-500</t>
-  </si>
-  <si>
-    <t>Nuclear large_ID14-500</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_ID14-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_ID14-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_ID14-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_ID14-500</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_w615581242-275</t>
-  </si>
-  <si>
-    <t>e_w615581242-275</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_w615581242-275</t>
-  </si>
-  <si>
-    <t>CCGT_w615581242-275</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_w615581242-275</t>
-  </si>
-  <si>
-    <t>Coal + CCS_w615581242-275</t>
-  </si>
-  <si>
-    <t>Gas turbine_w615581242-275</t>
-  </si>
-  <si>
-    <t>IGCC_w615581242-275</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_w615581242-275</t>
-  </si>
-  <si>
-    <t>Nuclear large_w615581242-275</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_w615581242-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_w615581242-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_w615581242-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_w615581242-275</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_ID37-500</t>
-  </si>
-  <si>
-    <t>e_ID37-500</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_ID37-500</t>
-  </si>
-  <si>
-    <t>CCGT_ID37-500</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_ID37-500</t>
-  </si>
-  <si>
-    <t>Coal + CCS_ID37-500</t>
-  </si>
-  <si>
-    <t>Gas turbine_ID37-500</t>
-  </si>
-  <si>
-    <t>IGCC_ID37-500</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_ID37-500</t>
-  </si>
-  <si>
-    <t>Nuclear large_ID37-500</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_ID37-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_ID37-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_ID37-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_ID37-500</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_w161965853-500</t>
-  </si>
-  <si>
-    <t>e_w161965853-500</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_w161965853-500</t>
-  </si>
-  <si>
-    <t>CCGT_w161965853-500</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_w161965853-500</t>
-  </si>
-  <si>
-    <t>Coal + CCS_w161965853-500</t>
-  </si>
-  <si>
-    <t>Gas turbine_w161965853-500</t>
-  </si>
-  <si>
-    <t>IGCC_w161965853-500</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_w161965853-500</t>
-  </si>
-  <si>
-    <t>Nuclear large_w161965853-500</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_w161965853-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_w161965853-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_w161965853-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_w161965853-500</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_ID8-275</t>
-  </si>
-  <si>
-    <t>e_ID8-275</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_ID8-275</t>
-  </si>
-  <si>
-    <t>CCGT_ID8-275</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_ID8-275</t>
-  </si>
-  <si>
-    <t>Coal + CCS_ID8-275</t>
-  </si>
-  <si>
-    <t>Gas turbine_ID8-275</t>
-  </si>
-  <si>
-    <t>IGCC_ID8-275</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_ID8-275</t>
-  </si>
-  <si>
-    <t>Nuclear large_ID8-275</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_ID8-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_ID8-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_ID8-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_ID8-275</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_w169444592-500</t>
-  </si>
-  <si>
-    <t>e_w169444592-500</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_w169444592-500</t>
-  </si>
-  <si>
-    <t>CCGT_w169444592-500</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_w169444592-500</t>
-  </si>
-  <si>
-    <t>Coal + CCS_w169444592-500</t>
-  </si>
-  <si>
-    <t>Gas turbine_w169444592-500</t>
-  </si>
-  <si>
-    <t>IGCC_w169444592-500</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_w169444592-500</t>
-  </si>
-  <si>
-    <t>Nuclear large_w169444592-500</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_w169444592-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_w169444592-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_w169444592-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_w169444592-500</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_ID10-500</t>
-  </si>
-  <si>
-    <t>e_ID10-500</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_ID10-500</t>
-  </si>
-  <si>
-    <t>CCGT_ID10-500</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_ID10-500</t>
-  </si>
-  <si>
-    <t>Coal + CCS_ID10-500</t>
-  </si>
-  <si>
-    <t>Gas turbine_ID10-500</t>
-  </si>
-  <si>
-    <t>IGCC_ID10-500</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_ID10-500</t>
-  </si>
-  <si>
-    <t>Nuclear large_ID10-500</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_ID10-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_ID10-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_ID10-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_ID10-500</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_ID11-500</t>
-  </si>
-  <si>
-    <t>e_ID11-500</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_ID11-500</t>
-  </si>
-  <si>
-    <t>CCGT_ID11-500</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_ID11-500</t>
-  </si>
-  <si>
-    <t>Coal + CCS_ID11-500</t>
-  </si>
-  <si>
-    <t>Gas turbine_ID11-500</t>
-  </si>
-  <si>
-    <t>IGCC_ID11-500</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_ID11-500</t>
-  </si>
-  <si>
-    <t>Nuclear large_ID11-500</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_ID11-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_ID11-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_ID11-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_ID11-500</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_ID30-500</t>
-  </si>
-  <si>
-    <t>e_ID30-500</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_ID30-500</t>
-  </si>
-  <si>
-    <t>CCGT_ID30-500</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_ID30-500</t>
-  </si>
-  <si>
-    <t>Coal + CCS_ID30-500</t>
-  </si>
-  <si>
-    <t>Gas turbine_ID30-500</t>
-  </si>
-  <si>
-    <t>IGCC_ID30-500</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_ID30-500</t>
-  </si>
-  <si>
-    <t>Nuclear large_ID30-500</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_ID30-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_ID30-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_ID30-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_ID30-500</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_w629512849-500</t>
-  </si>
-  <si>
-    <t>e_w629512849-500</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_w629512849-500</t>
-  </si>
-  <si>
-    <t>CCGT_w629512849-500</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_w629512849-500</t>
-  </si>
-  <si>
-    <t>Coal + CCS_w629512849-500</t>
-  </si>
-  <si>
-    <t>Gas turbine_w629512849-500</t>
-  </si>
-  <si>
-    <t>IGCC_w629512849-500</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_w629512849-500</t>
-  </si>
-  <si>
-    <t>Nuclear large_w629512849-500</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_w629512849-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_w629512849-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_w629512849-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_w629512849-500</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_ID29-500</t>
-  </si>
-  <si>
-    <t>e_ID29-500</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_ID29-500</t>
-  </si>
-  <si>
-    <t>CCGT_ID29-500</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_ID29-500</t>
-  </si>
-  <si>
-    <t>Coal + CCS_ID29-500</t>
-  </si>
-  <si>
-    <t>Gas turbine_ID29-500</t>
-  </si>
-  <si>
-    <t>IGCC_ID29-500</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_ID29-500</t>
-  </si>
-  <si>
-    <t>Nuclear large_ID29-500</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_ID29-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_ID29-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_ID29-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_ID29-500</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_w1013653012-500</t>
-  </si>
-  <si>
-    <t>e_w1013653012-500</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_w1013653012-500</t>
-  </si>
-  <si>
-    <t>CCGT_w1013653012-500</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_w1013653012-500</t>
-  </si>
-  <si>
-    <t>Coal + CCS_w1013653012-500</t>
-  </si>
-  <si>
-    <t>Gas turbine_w1013653012-500</t>
-  </si>
-  <si>
-    <t>IGCC_w1013653012-500</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_w1013653012-500</t>
-  </si>
-  <si>
-    <t>Nuclear large_w1013653012-500</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_w1013653012-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_w1013653012-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_w1013653012-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_w1013653012-500</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_ID1-275</t>
-  </si>
-  <si>
-    <t>e_ID1-275</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_ID1-275</t>
-  </si>
-  <si>
-    <t>CCGT_ID1-275</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_ID1-275</t>
-  </si>
-  <si>
-    <t>Coal + CCS_ID1-275</t>
-  </si>
-  <si>
-    <t>Gas turbine_ID1-275</t>
-  </si>
-  <si>
-    <t>IGCC_ID1-275</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_ID1-275</t>
-  </si>
-  <si>
-    <t>Nuclear large_ID1-275</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_ID1-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_ID1-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_ID1-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_ID1-275</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_w265318414-500</t>
-  </si>
-  <si>
-    <t>e_w265318414-500</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_w265318414-500</t>
-  </si>
-  <si>
-    <t>CCGT_w265318414-500</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_w265318414-500</t>
-  </si>
-  <si>
-    <t>Coal + CCS_w265318414-500</t>
-  </si>
-  <si>
-    <t>Gas turbine_w265318414-500</t>
-  </si>
-  <si>
-    <t>IGCC_w265318414-500</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_w265318414-500</t>
-  </si>
-  <si>
-    <t>Nuclear large_w265318414-500</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_w265318414-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_w265318414-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_w265318414-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_w265318414-500</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_w754073846-275</t>
-  </si>
-  <si>
-    <t>e_w754073846-275</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_w754073846-275</t>
-  </si>
-  <si>
-    <t>CCGT_w754073846-275</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_w754073846-275</t>
-  </si>
-  <si>
-    <t>Coal + CCS_w754073846-275</t>
-  </si>
-  <si>
-    <t>Gas turbine_w754073846-275</t>
-  </si>
-  <si>
-    <t>IGCC_w754073846-275</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_w754073846-275</t>
-  </si>
-  <si>
-    <t>Nuclear large_w754073846-275</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_w754073846-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_w754073846-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_w754073846-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_w754073846-275</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_w943539373-500</t>
-  </si>
-  <si>
-    <t>e_w943539373-500</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_w943539373-500</t>
-  </si>
-  <si>
-    <t>CCGT_w943539373-500</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_w943539373-500</t>
-  </si>
-  <si>
-    <t>Coal + CCS_w943539373-500</t>
-  </si>
-  <si>
-    <t>Gas turbine_w943539373-500</t>
-  </si>
-  <si>
-    <t>IGCC_w943539373-500</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_w943539373-500</t>
-  </si>
-  <si>
-    <t>Nuclear large_w943539373-500</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_w943539373-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_w943539373-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_w943539373-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_w943539373-500</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_ID27-500</t>
-  </si>
-  <si>
-    <t>e_ID27-500</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_ID27-500</t>
-  </si>
-  <si>
-    <t>CCGT_ID27-500</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_ID27-500</t>
-  </si>
-  <si>
-    <t>Coal + CCS_ID27-500</t>
-  </si>
-  <si>
-    <t>Gas turbine_ID27-500</t>
-  </si>
-  <si>
-    <t>IGCC_ID27-500</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_ID27-500</t>
-  </si>
-  <si>
-    <t>Nuclear large_ID27-500</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_ID27-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_ID27-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_ID27-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_ID27-500</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_w1316786278-275</t>
-  </si>
-  <si>
-    <t>e_w1316786278-275</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_w1316786278-275</t>
-  </si>
-  <si>
-    <t>CCGT_w1316786278-275</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_w1316786278-275</t>
-  </si>
-  <si>
-    <t>Coal + CCS_w1316786278-275</t>
-  </si>
-  <si>
-    <t>Gas turbine_w1316786278-275</t>
-  </si>
-  <si>
-    <t>IGCC_w1316786278-275</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_w1316786278-275</t>
-  </si>
-  <si>
-    <t>Nuclear large_w1316786278-275</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_w1316786278-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_w1316786278-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_w1316786278-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_w1316786278-275</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_w946191122-275</t>
-  </si>
-  <si>
-    <t>e_w946191122-275</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_w946191122-275</t>
-  </si>
-  <si>
-    <t>CCGT_w946191122-275</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_w946191122-275</t>
-  </si>
-  <si>
-    <t>Coal + CCS_w946191122-275</t>
-  </si>
-  <si>
-    <t>Gas turbine_w946191122-275</t>
-  </si>
-  <si>
-    <t>IGCC_w946191122-275</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_w946191122-275</t>
-  </si>
-  <si>
-    <t>Nuclear large_w946191122-275</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_w946191122-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_w946191122-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_w946191122-275</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_w946191122-275</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_w398909640-500</t>
-  </si>
-  <si>
-    <t>e_w398909640-500</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_w398909640-500</t>
-  </si>
-  <si>
-    <t>CCGT_w398909640-500</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_w398909640-500</t>
-  </si>
-  <si>
-    <t>Coal + CCS_w398909640-500</t>
-  </si>
-  <si>
-    <t>Gas turbine_w398909640-500</t>
-  </si>
-  <si>
-    <t>IGCC_w398909640-500</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_w398909640-500</t>
-  </si>
-  <si>
-    <t>Nuclear large_w398909640-500</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_w398909640-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_w398909640-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_w398909640-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_w398909640-500</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_ID28-500</t>
-  </si>
-  <si>
-    <t>e_ID28-500</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_ID28-500</t>
-  </si>
-  <si>
-    <t>CCGT_ID28-500</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_ID28-500</t>
-  </si>
-  <si>
-    <t>Coal + CCS_ID28-500</t>
-  </si>
-  <si>
-    <t>Gas turbine_ID28-500</t>
-  </si>
-  <si>
-    <t>IGCC_ID28-500</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_ID28-500</t>
-  </si>
-  <si>
-    <t>Nuclear large_ID28-500</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_ID28-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_ID28-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_ID28-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_ID28-500</t>
-  </si>
-  <si>
-    <t>Bioenergy + CCUS_w1186182648-500</t>
-  </si>
-  <si>
-    <t>e_w1186182648-500</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_w1186182648-500</t>
-  </si>
-  <si>
-    <t>CCGT_w1186182648-500</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_w1186182648-500</t>
-  </si>
-  <si>
-    <t>Coal + CCS_w1186182648-500</t>
-  </si>
-  <si>
-    <t>Gas turbine_w1186182648-500</t>
-  </si>
-  <si>
-    <t>IGCC_w1186182648-500</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_w1186182648-500</t>
-  </si>
-  <si>
-    <t>Nuclear large_w1186182648-500</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_w1186182648-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_w1186182648-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_w1186182648-500</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_w1186182648-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-1_w754178667-275</t>
-  </si>
-  <si>
-    <t>e_w754178667-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-2_w754178667-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-3_w754178667-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-1_w310695690-275</t>
-  </si>
-  <si>
-    <t>e_w310695690-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-2_w310695690-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-3_w310695690-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-1_w841499143-275</t>
-  </si>
-  <si>
-    <t>e_w841499143-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-2_w841499143-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-3_w841499143-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-1_w615581270-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-2_w615581270-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-3_w615581270-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-1_w615581232-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-2_w615581232-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-3_w615581232-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-1_w721674155-275</t>
-  </si>
-  <si>
-    <t>e_w721674155-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-2_w721674155-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-3_w721674155-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-1_w615581242-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-2_w615581242-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-3_w615581242-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-1_w399100035-500</t>
-  </si>
-  <si>
-    <t>e_w399100035-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-2_w399100035-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-3_w399100035-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-1_ID36-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-2_ID36-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-3_ID36-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-1_ID2-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-2_ID2-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-3_ID2-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-1_ID35-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-2_ID35-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-3_ID35-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-1_ID3-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-2_ID3-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-3_ID3-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-1_ID1-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-2_ID1-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-3_ID1-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-1_w310958602-275</t>
-  </si>
-  <si>
-    <t>e_w310958602-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-2_w310958602-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-3_w310958602-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-1_ID6-275</t>
-  </si>
-  <si>
-    <t>e_ID6-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-2_ID6-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-3_ID6-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-1_w314452486-500</t>
-  </si>
-  <si>
-    <t>e_w314452486-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-2_w314452486-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-3_w314452486-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-1_w721685825-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-2_w721685825-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-3_w721685825-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-1_w528189342-275</t>
-  </si>
-  <si>
-    <t>e_w528189342-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-2_w528189342-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-3_w528189342-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-1_ID31-500</t>
-  </si>
-  <si>
-    <t>e_ID31-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-2_ID31-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-3_ID31-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-1_w1193553154-275</t>
-  </si>
-  <si>
-    <t>e_w1193553154-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-2_w1193553154-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-3_w1193553154-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-1_w264550744-500</t>
-  </si>
-  <si>
-    <t>e_w264550744-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-2_w264550744-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-3_w264550744-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-1_w1316876158-275</t>
-  </si>
-  <si>
-    <t>e_w1316876158-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-2_w1316876158-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-3_w1316876158-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-1_w754178666-275</t>
-  </si>
-  <si>
-    <t>e_w754178666-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-2_w754178666-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-3_w754178666-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-1_w939542521-275</t>
-  </si>
-  <si>
-    <t>e_w939542521-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-2_w939542521-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-3_w939542521-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-1_w265318414-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-2_w265318414-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-3_w265318414-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-1_w614955993-230</t>
-  </si>
-  <si>
-    <t>e_w614955993-230</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-2_w614955993-230</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-3_w614955993-230</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-1_w340205049-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-2_w340205049-275</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IDN-3_w340205049-275</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w610198177-275</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w610198177-275</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w841499143-275</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w841499143-275</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w736595653-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w736595653-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w1186182648-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w1186182648-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w544403426-230</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w544403426-230</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w721685825-275</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w721685825-275</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w615581232-275</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w615581232-275</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_ID2-275</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_ID2-275</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_ID38-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_ID38-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w337039411-275</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w337039411-275</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w340205049-275</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w340205049-275</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_ID12-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_ID12-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w340978681-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w340978681-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_ID34-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_ID34-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w960747902-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w960747902-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w562061281-275</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w562061281-275</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_ID15-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_ID15-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_ID13-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_ID13-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_ID23-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_ID23-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w736595653-275</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w736595653-275</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_ID3-275</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_ID3-275</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w615581270-275</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w615581270-275</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w161960924-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w161960924-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w166633831-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w166633831-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_ID14-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_ID14-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w615581242-275</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w615581242-275</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_ID37-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_ID37-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w161965853-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w161965853-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_ID8-275</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_ID8-275</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w169444592-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w169444592-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_ID10-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_ID10-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_ID11-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_ID11-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_ID30-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_ID30-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w629512849-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w629512849-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_ID29-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_ID29-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w1013653012-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w1013653012-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_ID1-275</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_ID1-275</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w265318414-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w265318414-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w754073846-275</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w754073846-275</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w943539373-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w943539373-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_ID27-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_ID27-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w1316786278-275</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w1316786278-275</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w946191122-275</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w946191122-275</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w398909640-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w398909640-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_ID28-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_ID28-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w264550744-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w264550744-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w399100035-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w399100035-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w267626657-500</t>
-  </si>
-  <si>
-    <t>e_w267626657-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w267626657-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w528189342-275</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w528189342-275</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_ID31-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_ID31-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w931931133-275</t>
-  </si>
-  <si>
-    <t>e_w931931133-275</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w931931133-275</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_ID33-500</t>
-  </si>
-  <si>
-    <t>e_ID33-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_ID33-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w769617021-500</t>
-  </si>
-  <si>
-    <t>e_w769617021-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w769617021-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w314452486-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w314452486-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w1312287191-275</t>
-  </si>
-  <si>
-    <t>e_w1312287191-275</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w1312287191-275</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w1316876158-275</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w1316876158-275</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w721674155-275</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w721674155-275</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w469888049-275</t>
-  </si>
-  <si>
-    <t>e_w469888049-275</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w469888049-275</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w754178667-275</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w754178667-275</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w310695690-275</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w310695690-275</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_ID36-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_ID36-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_ID35-500</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_ID35-500</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w310958602-275</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w310958602-275</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_ID6-275</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_ID6-275</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w1193553154-275</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w1193553154-275</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w754178666-275</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w754178666-275</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w939542521-275</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w939542521-275</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w614955993-230</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w614955993-230</t>
+    <t>Bioenergy - Large scale unit_w610198177-275_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_w610198177-275_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_w610198177-275_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_w610198177-275_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_w610198177-275_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_w610198177-275_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_w610198177-275_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_w610198177-275_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_w610198177-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_w610198177-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_w610198177-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_w610198177-275_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_w544403426-230_IDN</t>
+  </si>
+  <si>
+    <t>e_w544403426-230_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_w544403426-230_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_w544403426-230_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_w544403426-230_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_w544403426-230_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_w544403426-230_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_w544403426-230_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_w544403426-230_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_w544403426-230_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_w544403426-230_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_w544403426-230_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_w544403426-230_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_w544403426-230_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_w721685825-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w721685825-275_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_w721685825-275_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_w721685825-275_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_w721685825-275_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_w721685825-275_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_w721685825-275_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_w721685825-275_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_w721685825-275_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_w721685825-275_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_w721685825-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_w721685825-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_w721685825-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_w721685825-275_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>e_ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_w337039411-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w337039411-275_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_w337039411-275_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_w337039411-275_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_w337039411-275_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_w337039411-275_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_w337039411-275_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_w337039411-275_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_w337039411-275_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_w337039411-275_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_w337039411-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_w337039411-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_w337039411-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_w337039411-275_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_w340205049-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w340205049-275_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_w340205049-275_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_w340205049-275_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_w340205049-275_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_w340205049-275_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_w340205049-275_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_w340205049-275_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_w340205049-275_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_w340205049-275_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_w340205049-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_w340205049-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_w340205049-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_w340205049-275_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_ID12-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID12-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_ID12-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_ID12-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_ID12-500_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_ID12-500_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_ID12-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_ID12-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_ID12-500_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_ID12-500_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_ID12-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_ID12-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_ID12-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_ID12-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_w340978681-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w340978681-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_w340978681-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_w340978681-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_w340978681-500_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_w340978681-500_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_w340978681-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_w340978681-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_w340978681-500_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_w340978681-500_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_w340978681-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_w340978681-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_w340978681-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_w340978681-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_ID34-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_ID34-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_ID34-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_ID34-500_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_ID34-500_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_ID34-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_ID34-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_ID34-500_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_ID34-500_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_ID34-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_ID34-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_ID34-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_ID34-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_w960747902-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w960747902-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_w960747902-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_w960747902-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_w960747902-500_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_w960747902-500_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_w960747902-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_w960747902-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_w960747902-500_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_w960747902-500_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_w960747902-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_w960747902-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_w960747902-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_w960747902-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_w562061281-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w562061281-275_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_w562061281-275_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_w562061281-275_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_w562061281-275_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_w562061281-275_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_w562061281-275_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_w562061281-275_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_w562061281-275_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_w562061281-275_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_w562061281-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_w562061281-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_w562061281-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_w562061281-275_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_ID15-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID15-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_ID15-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_ID15-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_ID15-500_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_ID15-500_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_ID15-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_ID15-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_ID15-500_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_ID15-500_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_ID15-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_ID15-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_ID15-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_ID15-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_ID13-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID13-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_ID13-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_ID13-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_ID13-500_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_ID13-500_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_ID13-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_ID13-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_ID13-500_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_ID13-500_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_ID13-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_ID13-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_ID13-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_ID13-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_ID23-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID23-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_ID23-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_ID23-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_ID23-500_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_ID23-500_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_ID23-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_ID23-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_ID23-500_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_ID23-500_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_ID23-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_ID23-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_ID23-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_ID23-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_w736595653-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w736595653-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_w736595653-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_w736595653-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_w736595653-500_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_w736595653-500_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_w736595653-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_w736595653-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_w736595653-500_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_w736595653-500_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_w736595653-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_w736595653-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_w736595653-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_w736595653-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_w736595653-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w736595653-275_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_w736595653-275_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_w736595653-275_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_w736595653-275_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_w736595653-275_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_w736595653-275_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_w736595653-275_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_w736595653-275_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_w736595653-275_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_w736595653-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_w736595653-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_w736595653-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_w736595653-275_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_ID3-275_IDN</t>
+  </si>
+  <si>
+    <t>e_ID3-275_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_ID3-275_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_ID3-275_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_ID3-275_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_ID3-275_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_ID3-275_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_ID3-275_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_ID3-275_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_ID3-275_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_ID3-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_ID3-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_ID3-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_ID3-275_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_w161960924-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_w161960924-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_w161960924-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_w161960924-500_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_w161960924-500_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_w161960924-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_w161960924-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_w161960924-500_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_w161960924-500_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_w161960924-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_w161960924-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_w161960924-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_w161960924-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_w166633831-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_w166633831-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_w166633831-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_w166633831-500_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_w166633831-500_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_w166633831-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_w166633831-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_w166633831-500_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_w166633831-500_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_w166633831-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_w166633831-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_w166633831-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_w166633831-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_ID14-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID14-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_ID14-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_ID14-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_ID14-500_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_ID14-500_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_ID14-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_ID14-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_ID14-500_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_ID14-500_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_ID14-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_ID14-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_ID14-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_ID14-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_w615581242-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581242-275_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_w615581242-275_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_w615581242-275_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_w615581242-275_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_w615581242-275_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_w615581242-275_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_w615581242-275_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_w615581242-275_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_w615581242-275_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_w615581242-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_w615581242-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_w615581242-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_w615581242-275_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_ID37-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID37-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_ID37-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_ID37-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_ID37-500_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_ID37-500_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_ID37-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_ID37-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_ID37-500_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_ID37-500_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_ID37-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_ID37-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_ID37-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_ID37-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_w161965853-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w161965853-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_w161965853-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_w161965853-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_w161965853-500_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_w161965853-500_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_w161965853-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_w161965853-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_w161965853-500_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_w161965853-500_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_w161965853-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_w161965853-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_w161965853-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_w161965853-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_ID8-275_IDN</t>
+  </si>
+  <si>
+    <t>e_ID8-275_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_ID8-275_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_ID8-275_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_ID8-275_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_ID8-275_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_ID8-275_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_ID8-275_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_ID8-275_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_ID8-275_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_ID8-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_ID8-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_ID8-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_ID8-275_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_w169444592-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w169444592-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_w169444592-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_w169444592-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_w169444592-500_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_w169444592-500_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_w169444592-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_w169444592-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_w169444592-500_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_w169444592-500_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_w169444592-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_w169444592-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_w169444592-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_w169444592-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_ID10-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID10-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_ID10-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_ID10-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_ID10-500_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_ID10-500_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_ID10-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_ID10-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_ID10-500_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_ID10-500_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_ID10-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_ID10-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_ID10-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_ID10-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_ID11-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID11-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_ID11-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_ID11-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_ID11-500_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_ID11-500_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_ID11-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_ID11-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_ID11-500_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_ID11-500_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_ID11-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_ID11-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_ID11-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_ID11-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_ID30-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID30-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_ID30-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_ID30-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_ID30-500_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_ID30-500_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_ID30-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_ID30-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_ID30-500_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_ID30-500_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_ID30-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_ID30-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_ID30-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_ID30-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_w629512849-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w629512849-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_w629512849-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_w629512849-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_w629512849-500_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_w629512849-500_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_w629512849-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_w629512849-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_w629512849-500_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_w629512849-500_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_w629512849-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_w629512849-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_w629512849-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_w629512849-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_ID29-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID29-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_ID29-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_ID29-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_ID29-500_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_ID29-500_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_ID29-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_ID29-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_ID29-500_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_ID29-500_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_ID29-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_ID29-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_ID29-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_ID29-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_w1013653012-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w1013653012-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_w1013653012-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_w1013653012-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_w1013653012-500_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_w1013653012-500_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_w1013653012-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_w1013653012-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_w1013653012-500_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_w1013653012-500_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_w1013653012-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_w1013653012-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_w1013653012-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_w1013653012-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_ID1-275_IDN</t>
+  </si>
+  <si>
+    <t>e_ID1-275_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_ID1-275_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_ID1-275_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_ID1-275_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_ID1-275_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_ID1-275_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_ID1-275_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_ID1-275_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_ID1-275_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_ID1-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_ID1-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_ID1-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_ID1-275_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_w265318414-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w265318414-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_w265318414-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_w265318414-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_w265318414-500_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_w265318414-500_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_w265318414-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_w265318414-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_w265318414-500_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_w265318414-500_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_w265318414-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_w265318414-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_w265318414-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_w265318414-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_w754073846-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w754073846-275_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_w754073846-275_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_w754073846-275_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_w754073846-275_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_w754073846-275_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_w754073846-275_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_w754073846-275_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_w754073846-275_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_w754073846-275_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_w754073846-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_w754073846-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_w754073846-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_w754073846-275_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_w943539373-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w943539373-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_w943539373-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_w943539373-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_w943539373-500_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_w943539373-500_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_w943539373-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_w943539373-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_w943539373-500_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_w943539373-500_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_w943539373-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_w943539373-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_w943539373-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_w943539373-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_ID27-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID27-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_ID27-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_ID27-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_ID27-500_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_ID27-500_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_ID27-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_ID27-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_ID27-500_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_ID27-500_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_ID27-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_ID27-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_ID27-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_ID27-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_w1316786278-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w1316786278-275_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_w1316786278-275_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_w1316786278-275_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_w1316786278-275_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_w1316786278-275_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_w1316786278-275_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_w1316786278-275_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_w1316786278-275_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_w1316786278-275_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_w1316786278-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_w1316786278-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_w1316786278-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_w1316786278-275_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_w946191122-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w946191122-275_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_w946191122-275_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_w946191122-275_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_w946191122-275_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_w946191122-275_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_w946191122-275_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_w946191122-275_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_w946191122-275_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_w946191122-275_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_w946191122-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_w946191122-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_w946191122-275_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_w946191122-275_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_w398909640-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w398909640-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_w398909640-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_w398909640-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_w398909640-500_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_w398909640-500_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_w398909640-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_w398909640-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_w398909640-500_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_w398909640-500_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_w398909640-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_w398909640-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_w398909640-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_w398909640-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_ID28-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID28-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_ID28-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_ID28-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_ID28-500_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_ID28-500_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_ID28-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_ID28-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_ID28-500_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_ID28-500_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_ID28-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_ID28-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_ID28-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_ID28-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS_w1186182648-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w1186182648-500_IDN</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_w1186182648-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT_w1186182648-500_IDN</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_w1186182648-500_IDN</t>
+  </si>
+  <si>
+    <t>Coal + CCS_w1186182648-500_IDN</t>
+  </si>
+  <si>
+    <t>Gas turbine_w1186182648-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC_w1186182648-500_IDN</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_w1186182648-500_IDN</t>
+  </si>
+  <si>
+    <t>Nuclear large_w1186182648-500_IDN</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_w1186182648-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_w1186182648-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_w1186182648-500_IDN</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_w1186182648-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-1_w754178667-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w754178667-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-2_w754178667-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-3_w754178667-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-1_w310695690-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w310695690-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-2_w310695690-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-3_w310695690-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-1_w841499143-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w841499143-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-2_w841499143-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-3_w841499143-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-1_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-2_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-3_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-1_w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-2_w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-3_w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-1_w721674155-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w721674155-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-2_w721674155-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-3_w721674155-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-1_w615581242-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-2_w615581242-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-3_w615581242-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-1_w399100035-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w399100035-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-2_w399100035-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-3_w399100035-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-1_ID36-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-2_ID36-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-3_ID36-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-1_ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-2_ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-3_ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-1_ID35-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-2_ID35-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-3_ID35-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-1_ID3-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-2_ID3-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-3_ID3-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-1_ID1-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-2_ID1-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-3_ID1-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-1_w310958602-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w310958602-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-2_w310958602-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-3_w310958602-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-1_ID6-275_IDN</t>
+  </si>
+  <si>
+    <t>e_ID6-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-2_ID6-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-3_ID6-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-1_w314452486-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w314452486-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-2_w314452486-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-3_w314452486-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-1_w721685825-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-2_w721685825-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-3_w721685825-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-1_w528189342-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w528189342-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-2_w528189342-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-3_w528189342-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-1_ID31-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID31-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-2_ID31-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-3_ID31-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-1_w1193553154-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w1193553154-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-2_w1193553154-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-3_w1193553154-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-1_w264550744-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w264550744-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-2_w264550744-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-3_w264550744-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-1_w1316876158-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w1316876158-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-2_w1316876158-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-3_w1316876158-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-1_w754178666-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w754178666-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-2_w754178666-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-3_w754178666-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-1_w939542521-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w939542521-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-2_w939542521-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-3_w939542521-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-1_w265318414-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-2_w265318414-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-3_w265318414-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-1_w614955993-230_IDN</t>
+  </si>
+  <si>
+    <t>e_w614955993-230_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-2_w614955993-230_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-3_w614955993-230_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-1_w340205049-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-2_w340205049-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_Hydro_IDN-3_w340205049-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w610198177-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w610198177-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w841499143-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w841499143-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w736595653-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w736595653-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w1186182648-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w1186182648-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w544403426-230_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w544403426-230_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w721685825-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w721685825-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w337039411-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w337039411-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w340205049-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w340205049-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_ID12-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_ID12-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w340978681-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w340978681-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_ID34-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_ID34-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w960747902-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w960747902-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w562061281-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w562061281-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_ID15-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_ID15-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_ID13-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_ID13-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_ID23-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_ID23-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w736595653-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w736595653-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_ID3-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_ID3-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w161960924-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w161960924-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w166633831-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w166633831-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_ID14-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_ID14-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w615581242-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w615581242-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_ID37-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_ID37-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w161965853-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w161965853-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_ID8-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_ID8-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w169444592-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w169444592-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_ID10-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_ID10-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_ID11-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_ID11-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_ID30-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_ID30-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w629512849-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w629512849-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_ID29-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_ID29-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w1013653012-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w1013653012-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_ID1-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_ID1-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w265318414-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w265318414-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w754073846-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w754073846-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w943539373-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w943539373-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_ID27-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_ID27-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w1316786278-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w1316786278-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w946191122-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w946191122-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w398909640-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w398909640-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_ID28-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_ID28-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w264550744-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w264550744-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w399100035-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w399100035-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w267626657-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w267626657-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w267626657-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w528189342-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w528189342-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_ID31-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_ID31-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w931931133-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w931931133-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w931931133-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_ID33-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID33-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_ID33-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w769617021-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w769617021-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w769617021-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w314452486-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w314452486-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w1312287191-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w1312287191-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w1312287191-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w1316876158-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w1316876158-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w721674155-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w721674155-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w469888049-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w469888049-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w469888049-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w754178667-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w754178667-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w310695690-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w310695690-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_ID36-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_ID36-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_ID35-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_ID35-500_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w310958602-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w310958602-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_ID6-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_ID6-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w1193553154-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w1193553154-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w754178666-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w754178666-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w939542521-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w939542521-275_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w614955993-230_IDN</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w614955993-230_IDN</t>
   </si>
   <si>
     <t>ELC</t>
@@ -4111,7 +4111,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{207BB9A1-0E74-41CC-8AA8-DA562BD0C320}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0283EB3A-7D99-47FA-8F0E-C7214A9DD90B}">
   <dimension ref="B2:AF792"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -17574,7 +17574,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF53336A-87E2-46F7-8419-29A0E4231EE6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04116824-16A8-4A92-8DDF-75F4DF5F2AA7}">
   <dimension ref="B9:L36"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IDN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEC6CF58-5BC5-43EE-9D91-53EF73E9309B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5F6604F-A522-4F5C-924F-AC7CEF709178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4156,7 +4156,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DBF61A6-2EB8-43B7-A40F-389C55C299FE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEAD587D-2A93-4B39-8112-6CD51A837CFC}">
   <dimension ref="B2:AF792"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -18003,7 +18003,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C13236C9-E064-4210-9A9F-5DD0F6B547A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{450CAF18-BCEE-4024-8067-80FFCC8D0D0E}">
   <dimension ref="B9:L36"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
